--- a/filesystem/Finance/Billing/FenwickGenomics_Dec2025_statement.xlsx
+++ b/filesystem/Finance/Billing/FenwickGenomics_Dec2025_statement.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="31">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -188,6 +188,11 @@
       <name val="Segoe UI"/>
       <color rgb="002563EB"/>
       <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="FF334155"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="12">
@@ -255,7 +260,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="39">
     <border>
       <left/>
       <right/>
@@ -503,11 +508,219 @@
         <color rgb="00E2E8F0"/>
       </bottom>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="001E293B"/>
+      </left>
+      <right style="medium">
+        <color rgb="001E293B"/>
+      </right>
+      <top style="medium">
+        <color rgb="001E293B"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="001E293B"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="001E293B"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="001E293B"/>
+      </right>
+      <top style="medium">
+        <color rgb="001E293B"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="001E293B"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="001E293B"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="001E293B"/>
+      </right>
+      <top style="medium">
+        <color rgb="001E293B"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="001E293B"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00A6A6A6"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00A6A6A6"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="double">
+        <color rgb="000F172A"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00A6A6A6"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="double">
+        <color rgb="000F172A"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F59E0B"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00A6A6A6"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F59E0B"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F59E0B"/>
+      </top>
+      <bottom style="double">
+        <color rgb="00B45309"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00A6A6A6"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F59E0B"/>
+      </top>
+      <bottom style="double">
+        <color rgb="00B45309"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002563EB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -706,6 +919,27 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1032,13 +1266,6 @@
           <t>Thornfield Life Sciences Marketing, Inc.</t>
         </is>
       </c>
-      <c r="B1" s="18" t="n"/>
-      <c r="C1" s="18" t="n"/>
-      <c r="D1" s="18" t="n"/>
-      <c r="E1" s="18" t="n"/>
-      <c r="F1" s="18" t="n"/>
-      <c r="G1" s="18" t="n"/>
-      <c r="H1" s="18" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="19" t="inlineStr">
@@ -1046,13 +1273,6 @@
           <t>Monthly Billing Statement</t>
         </is>
       </c>
-      <c r="B2" s="19" t="n"/>
-      <c r="C2" s="19" t="n"/>
-      <c r="D2" s="19" t="n"/>
-      <c r="E2" s="19" t="n"/>
-      <c r="F2" s="19" t="n"/>
-      <c r="G2" s="19" t="n"/>
-      <c r="H2" s="19" t="n"/>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="20" t="inlineStr">
@@ -1060,13 +1280,6 @@
           <t>227 Alexander Drive, Suite 400</t>
         </is>
       </c>
-      <c r="B3" s="20" t="n"/>
-      <c r="C3" s="20" t="n"/>
-      <c r="D3" s="20" t="n"/>
-      <c r="E3" s="20" t="n"/>
-      <c r="F3" s="20" t="n"/>
-      <c r="G3" s="20" t="n"/>
-      <c r="H3" s="20" t="n"/>
     </row>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="20" t="inlineStr">
@@ -1074,13 +1287,6 @@
           <t>Durham, NC 27709</t>
         </is>
       </c>
-      <c r="B4" s="20" t="n"/>
-      <c r="C4" s="20" t="n"/>
-      <c r="D4" s="20" t="n"/>
-      <c r="E4" s="20" t="n"/>
-      <c r="F4" s="20" t="n"/>
-      <c r="G4" s="20" t="n"/>
-      <c r="H4" s="20" t="n"/>
     </row>
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="20" t="inlineStr">
@@ -1088,13 +1294,6 @@
           <t>EIN: 47-3812905</t>
         </is>
       </c>
-      <c r="B5" s="20" t="n"/>
-      <c r="C5" s="20" t="n"/>
-      <c r="D5" s="20" t="n"/>
-      <c r="E5" s="20" t="n"/>
-      <c r="F5" s="20" t="n"/>
-      <c r="G5" s="20" t="n"/>
-      <c r="H5" s="20" t="n"/>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="20" t="inlineStr">
@@ -1102,13 +1301,6 @@
           <t>Phone: +1 (919) 555-0142</t>
         </is>
       </c>
-      <c r="B6" s="20" t="n"/>
-      <c r="C6" s="20" t="n"/>
-      <c r="D6" s="20" t="n"/>
-      <c r="E6" s="20" t="n"/>
-      <c r="F6" s="20" t="n"/>
-      <c r="G6" s="20" t="n"/>
-      <c r="H6" s="20" t="n"/>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="20" t="inlineStr">
@@ -1116,28 +1308,21 @@
           <t>billing@thornfieldlsm.com</t>
         </is>
       </c>
-      <c r="B7" s="20" t="n"/>
-      <c r="C7" s="20" t="n"/>
-      <c r="D7" s="20" t="n"/>
-      <c r="E7" s="20" t="n"/>
-      <c r="F7" s="20" t="n"/>
-      <c r="G7" s="20" t="n"/>
-      <c r="H7" s="20" t="n"/>
     </row>
     <row r="8" ht="12" customHeight="1"/>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="21" t="inlineStr">
+      <c r="A9" s="68" t="inlineStr">
         <is>
           <t>Statement</t>
         </is>
       </c>
-      <c r="B9" s="22" t="n"/>
-      <c r="C9" s="22" t="n"/>
-      <c r="D9" s="22" t="n"/>
-      <c r="E9" s="22" t="n"/>
-      <c r="F9" s="22" t="n"/>
-      <c r="G9" s="22" t="n"/>
-      <c r="H9" s="23" t="n"/>
+      <c r="B9" s="69" t="n"/>
+      <c r="C9" s="69" t="n"/>
+      <c r="D9" s="69" t="n"/>
+      <c r="E9" s="69" t="n"/>
+      <c r="F9" s="69" t="n"/>
+      <c r="G9" s="69" t="n"/>
+      <c r="H9" s="70" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
@@ -1150,12 +1335,12 @@
           <t>STMT-2025-12-0198</t>
         </is>
       </c>
-      <c r="C10" s="26" t="n"/>
-      <c r="D10" s="26" t="n"/>
-      <c r="E10" s="26" t="n"/>
-      <c r="F10" s="26" t="n"/>
-      <c r="G10" s="26" t="n"/>
-      <c r="H10" s="27" t="n"/>
+      <c r="C10" s="71" t="n"/>
+      <c r="D10" s="71" t="n"/>
+      <c r="E10" s="71" t="n"/>
+      <c r="F10" s="71" t="n"/>
+      <c r="G10" s="71" t="n"/>
+      <c r="H10" s="72" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
@@ -1168,12 +1353,12 @@
           <t>12/01/2025</t>
         </is>
       </c>
-      <c r="C11" s="26" t="n"/>
-      <c r="D11" s="26" t="n"/>
-      <c r="E11" s="26" t="n"/>
-      <c r="F11" s="26" t="n"/>
-      <c r="G11" s="26" t="n"/>
-      <c r="H11" s="27" t="n"/>
+      <c r="C11" s="71" t="n"/>
+      <c r="D11" s="71" t="n"/>
+      <c r="E11" s="71" t="n"/>
+      <c r="F11" s="71" t="n"/>
+      <c r="G11" s="71" t="n"/>
+      <c r="H11" s="72" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
@@ -1186,12 +1371,12 @@
           <t>12/01/2025 – 12/31/2025</t>
         </is>
       </c>
-      <c r="C12" s="26" t="n"/>
-      <c r="D12" s="26" t="n"/>
-      <c r="E12" s="26" t="n"/>
-      <c r="F12" s="26" t="n"/>
-      <c r="G12" s="26" t="n"/>
-      <c r="H12" s="27" t="n"/>
+      <c r="C12" s="71" t="n"/>
+      <c r="D12" s="71" t="n"/>
+      <c r="E12" s="71" t="n"/>
+      <c r="F12" s="71" t="n"/>
+      <c r="G12" s="71" t="n"/>
+      <c r="H12" s="72" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
@@ -1204,12 +1389,12 @@
           <t>December 2025</t>
         </is>
       </c>
-      <c r="C13" s="26" t="n"/>
-      <c r="D13" s="26" t="n"/>
-      <c r="E13" s="26" t="n"/>
-      <c r="F13" s="26" t="n"/>
-      <c r="G13" s="26" t="n"/>
-      <c r="H13" s="27" t="n"/>
+      <c r="C13" s="71" t="n"/>
+      <c r="D13" s="71" t="n"/>
+      <c r="E13" s="71" t="n"/>
+      <c r="F13" s="71" t="n"/>
+      <c r="G13" s="71" t="n"/>
+      <c r="H13" s="72" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
@@ -1222,12 +1407,12 @@
           <t>Net 30</t>
         </is>
       </c>
-      <c r="C14" s="26" t="n"/>
-      <c r="D14" s="26" t="n"/>
-      <c r="E14" s="26" t="n"/>
-      <c r="F14" s="26" t="n"/>
-      <c r="G14" s="26" t="n"/>
-      <c r="H14" s="27" t="n"/>
+      <c r="C14" s="71" t="n"/>
+      <c r="D14" s="71" t="n"/>
+      <c r="E14" s="71" t="n"/>
+      <c r="F14" s="71" t="n"/>
+      <c r="G14" s="71" t="n"/>
+      <c r="H14" s="72" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
@@ -1240,27 +1425,27 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="C15" s="26" t="n"/>
-      <c r="D15" s="26" t="n"/>
-      <c r="E15" s="26" t="n"/>
-      <c r="F15" s="26" t="n"/>
-      <c r="G15" s="26" t="n"/>
-      <c r="H15" s="27" t="n"/>
+      <c r="C15" s="71" t="n"/>
+      <c r="D15" s="71" t="n"/>
+      <c r="E15" s="71" t="n"/>
+      <c r="F15" s="71" t="n"/>
+      <c r="G15" s="71" t="n"/>
+      <c r="H15" s="72" t="n"/>
     </row>
     <row r="16" ht="12" customHeight="1"/>
     <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="21" t="inlineStr">
+      <c r="A17" s="68" t="inlineStr">
         <is>
           <t>Bill To</t>
         </is>
       </c>
-      <c r="B17" s="22" t="n"/>
-      <c r="C17" s="22" t="n"/>
-      <c r="D17" s="22" t="n"/>
-      <c r="E17" s="22" t="n"/>
-      <c r="F17" s="22" t="n"/>
-      <c r="G17" s="22" t="n"/>
-      <c r="H17" s="23" t="n"/>
+      <c r="B17" s="69" t="n"/>
+      <c r="C17" s="69" t="n"/>
+      <c r="D17" s="69" t="n"/>
+      <c r="E17" s="69" t="n"/>
+      <c r="F17" s="69" t="n"/>
+      <c r="G17" s="69" t="n"/>
+      <c r="H17" s="70" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
@@ -1273,12 +1458,12 @@
           <t>Fenwick Genomics, Inc.</t>
         </is>
       </c>
-      <c r="C18" s="26" t="n"/>
-      <c r="D18" s="26" t="n"/>
-      <c r="E18" s="26" t="n"/>
-      <c r="F18" s="26" t="n"/>
-      <c r="G18" s="26" t="n"/>
-      <c r="H18" s="27" t="n"/>
+      <c r="C18" s="71" t="n"/>
+      <c r="D18" s="71" t="n"/>
+      <c r="E18" s="71" t="n"/>
+      <c r="F18" s="71" t="n"/>
+      <c r="G18" s="71" t="n"/>
+      <c r="H18" s="72" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
@@ -1291,12 +1476,12 @@
           <t>Waltham, MA</t>
         </is>
       </c>
-      <c r="C19" s="26" t="n"/>
-      <c r="D19" s="26" t="n"/>
-      <c r="E19" s="26" t="n"/>
-      <c r="F19" s="26" t="n"/>
-      <c r="G19" s="26" t="n"/>
-      <c r="H19" s="27" t="n"/>
+      <c r="C19" s="71" t="n"/>
+      <c r="D19" s="71" t="n"/>
+      <c r="E19" s="71" t="n"/>
+      <c r="F19" s="71" t="n"/>
+      <c r="G19" s="71" t="n"/>
+      <c r="H19" s="72" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
@@ -1309,12 +1494,12 @@
           <t>CUST-2025-0198</t>
         </is>
       </c>
-      <c r="C20" s="26" t="n"/>
-      <c r="D20" s="26" t="n"/>
-      <c r="E20" s="26" t="n"/>
-      <c r="F20" s="26" t="n"/>
-      <c r="G20" s="26" t="n"/>
-      <c r="H20" s="27" t="n"/>
+      <c r="C20" s="71" t="n"/>
+      <c r="D20" s="71" t="n"/>
+      <c r="E20" s="71" t="n"/>
+      <c r="F20" s="71" t="n"/>
+      <c r="G20" s="71" t="n"/>
+      <c r="H20" s="72" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
@@ -1327,12 +1512,12 @@
           <t>Inherited — Bramwell</t>
         </is>
       </c>
-      <c r="C21" s="26" t="n"/>
-      <c r="D21" s="26" t="n"/>
-      <c r="E21" s="26" t="n"/>
-      <c r="F21" s="26" t="n"/>
-      <c r="G21" s="26" t="n"/>
-      <c r="H21" s="27" t="n"/>
+      <c r="C21" s="71" t="n"/>
+      <c r="D21" s="71" t="n"/>
+      <c r="E21" s="71" t="n"/>
+      <c r="F21" s="71" t="n"/>
+      <c r="G21" s="71" t="n"/>
+      <c r="H21" s="72" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
@@ -1345,12 +1530,12 @@
           <t>SO-2025-0417</t>
         </is>
       </c>
-      <c r="C22" s="26" t="n"/>
-      <c r="D22" s="26" t="n"/>
-      <c r="E22" s="26" t="n"/>
-      <c r="F22" s="26" t="n"/>
-      <c r="G22" s="26" t="n"/>
-      <c r="H22" s="27" t="n"/>
+      <c r="C22" s="71" t="n"/>
+      <c r="D22" s="71" t="n"/>
+      <c r="E22" s="71" t="n"/>
+      <c r="F22" s="71" t="n"/>
+      <c r="G22" s="71" t="n"/>
+      <c r="H22" s="72" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="24" t="inlineStr">
@@ -1363,27 +1548,27 @@
           <t>04/01/2025 – 03/31/2026</t>
         </is>
       </c>
-      <c r="C23" s="26" t="n"/>
-      <c r="D23" s="26" t="n"/>
-      <c r="E23" s="26" t="n"/>
-      <c r="F23" s="26" t="n"/>
-      <c r="G23" s="26" t="n"/>
-      <c r="H23" s="27" t="n"/>
+      <c r="C23" s="71" t="n"/>
+      <c r="D23" s="71" t="n"/>
+      <c r="E23" s="71" t="n"/>
+      <c r="F23" s="71" t="n"/>
+      <c r="G23" s="71" t="n"/>
+      <c r="H23" s="72" t="n"/>
     </row>
     <row r="24" ht="12" customHeight="1"/>
     <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="21" t="inlineStr">
+      <c r="A25" s="68" t="inlineStr">
         <is>
           <t>Line Items</t>
         </is>
       </c>
-      <c r="B25" s="22" t="n"/>
-      <c r="C25" s="22" t="n"/>
-      <c r="D25" s="22" t="n"/>
-      <c r="E25" s="22" t="n"/>
-      <c r="F25" s="22" t="n"/>
-      <c r="G25" s="22" t="n"/>
-      <c r="H25" s="23" t="n"/>
+      <c r="B25" s="69" t="n"/>
+      <c r="C25" s="69" t="n"/>
+      <c r="D25" s="69" t="n"/>
+      <c r="E25" s="69" t="n"/>
+      <c r="F25" s="69" t="n"/>
+      <c r="G25" s="69" t="n"/>
+      <c r="H25" s="70" t="n"/>
     </row>
     <row r="26" ht="28" customHeight="1">
       <c r="A26" s="28" t="inlineStr">
@@ -1496,7 +1681,7 @@
       <c r="F28" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="G28" s="40" t="inlineStr">
+      <c r="G28" s="73" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1536,7 +1721,7 @@
       <c r="F29" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="G29" s="42" t="inlineStr">
+      <c r="G29" s="74" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1576,7 +1761,7 @@
       <c r="F30" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="G30" s="40" t="inlineStr">
+      <c r="G30" s="73" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1616,7 +1801,7 @@
       <c r="F31" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="G31" s="42" t="inlineStr">
+      <c r="G31" s="74" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1656,7 +1841,7 @@
       <c r="F32" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="G32" s="40" t="inlineStr">
+      <c r="G32" s="73" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1696,7 +1881,7 @@
       <c r="F33" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="G33" s="42" t="inlineStr">
+      <c r="G33" s="74" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1736,7 +1921,7 @@
       <c r="F34" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="G34" s="40" t="inlineStr">
+      <c r="G34" s="73" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1749,18 +1934,18 @@
     </row>
     <row r="35" ht="12" customHeight="1"/>
     <row r="36" ht="26" customHeight="1">
-      <c r="A36" s="21" t="inlineStr">
+      <c r="A36" s="68" t="inlineStr">
         <is>
           <t>Statement Total</t>
         </is>
       </c>
-      <c r="B36" s="22" t="n"/>
-      <c r="C36" s="22" t="n"/>
-      <c r="D36" s="22" t="n"/>
-      <c r="E36" s="22" t="n"/>
-      <c r="F36" s="22" t="n"/>
-      <c r="G36" s="22" t="n"/>
-      <c r="H36" s="23" t="n"/>
+      <c r="B36" s="69" t="n"/>
+      <c r="C36" s="69" t="n"/>
+      <c r="D36" s="69" t="n"/>
+      <c r="E36" s="69" t="n"/>
+      <c r="F36" s="69" t="n"/>
+      <c r="G36" s="69" t="n"/>
+      <c r="H36" s="70" t="n"/>
     </row>
     <row r="37" ht="23" customHeight="1">
       <c r="A37" s="43" t="inlineStr">
@@ -1768,15 +1953,15 @@
           <t>Subtotal — Retainer</t>
         </is>
       </c>
-      <c r="B37" s="44" t="n"/>
-      <c r="C37" s="44" t="n"/>
-      <c r="D37" s="44" t="n"/>
-      <c r="E37" s="45" t="n"/>
+      <c r="B37" s="71" t="n"/>
+      <c r="C37" s="71" t="n"/>
+      <c r="D37" s="71" t="n"/>
+      <c r="E37" s="72" t="n"/>
       <c r="F37" s="46" t="n">
         <v>8500</v>
       </c>
-      <c r="G37" s="47" t="n"/>
-      <c r="H37" s="48" t="n"/>
+      <c r="G37" s="71" t="n"/>
+      <c r="H37" s="72" t="n"/>
     </row>
     <row r="38" ht="23" customHeight="1">
       <c r="A38" s="43" t="inlineStr">
@@ -1784,15 +1969,15 @@
           <t>Subtotal — Reimbursables</t>
         </is>
       </c>
-      <c r="B38" s="44" t="n"/>
-      <c r="C38" s="44" t="n"/>
-      <c r="D38" s="44" t="n"/>
-      <c r="E38" s="45" t="n"/>
+      <c r="B38" s="71" t="n"/>
+      <c r="C38" s="71" t="n"/>
+      <c r="D38" s="71" t="n"/>
+      <c r="E38" s="72" t="n"/>
       <c r="F38" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="G38" s="47" t="n"/>
-      <c r="H38" s="48" t="n"/>
+      <c r="G38" s="71" t="n"/>
+      <c r="H38" s="72" t="n"/>
     </row>
     <row r="39" ht="23" customHeight="1">
       <c r="A39" s="43" t="inlineStr">
@@ -1800,15 +1985,15 @@
           <t>Adjustments</t>
         </is>
       </c>
-      <c r="B39" s="44" t="n"/>
-      <c r="C39" s="44" t="n"/>
-      <c r="D39" s="44" t="n"/>
-      <c r="E39" s="45" t="n"/>
+      <c r="B39" s="71" t="n"/>
+      <c r="C39" s="71" t="n"/>
+      <c r="D39" s="71" t="n"/>
+      <c r="E39" s="72" t="n"/>
       <c r="F39" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="G39" s="47" t="n"/>
-      <c r="H39" s="48" t="n"/>
+      <c r="G39" s="71" t="n"/>
+      <c r="H39" s="72" t="n"/>
     </row>
     <row r="40" ht="23" customHeight="1">
       <c r="A40" s="49" t="inlineStr">
@@ -1816,15 +2001,15 @@
           <t>Total Due for December 2025</t>
         </is>
       </c>
-      <c r="B40" s="50" t="n"/>
-      <c r="C40" s="50" t="n"/>
-      <c r="D40" s="50" t="n"/>
-      <c r="E40" s="51" t="n"/>
+      <c r="B40" s="75" t="n"/>
+      <c r="C40" s="75" t="n"/>
+      <c r="D40" s="75" t="n"/>
+      <c r="E40" s="76" t="n"/>
       <c r="F40" s="52" t="n">
         <v>8500</v>
       </c>
-      <c r="G40" s="53" t="n"/>
-      <c r="H40" s="54" t="n"/>
+      <c r="G40" s="75" t="n"/>
+      <c r="H40" s="76" t="n"/>
     </row>
     <row r="41" ht="23" customHeight="1">
       <c r="A41" s="43" t="inlineStr">
@@ -1832,15 +2017,15 @@
           <t>Payments Received</t>
         </is>
       </c>
-      <c r="B41" s="44" t="n"/>
-      <c r="C41" s="44" t="n"/>
-      <c r="D41" s="44" t="n"/>
-      <c r="E41" s="45" t="n"/>
+      <c r="B41" s="71" t="n"/>
+      <c r="C41" s="71" t="n"/>
+      <c r="D41" s="71" t="n"/>
+      <c r="E41" s="72" t="n"/>
       <c r="F41" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="G41" s="47" t="n"/>
-      <c r="H41" s="48" t="n"/>
+      <c r="G41" s="71" t="n"/>
+      <c r="H41" s="72" t="n"/>
     </row>
     <row r="42" ht="23" customHeight="1">
       <c r="A42" s="55" t="inlineStr">
@@ -1848,45 +2033,45 @@
           <t>Balance</t>
         </is>
       </c>
-      <c r="B42" s="56" t="n"/>
-      <c r="C42" s="56" t="n"/>
-      <c r="D42" s="56" t="n"/>
-      <c r="E42" s="57" t="n"/>
+      <c r="B42" s="77" t="n"/>
+      <c r="C42" s="77" t="n"/>
+      <c r="D42" s="77" t="n"/>
+      <c r="E42" s="78" t="n"/>
       <c r="F42" s="58" t="n">
         <v>8500</v>
       </c>
-      <c r="G42" s="59" t="n"/>
-      <c r="H42" s="60" t="n"/>
+      <c r="G42" s="77" t="n"/>
+      <c r="H42" s="78" t="n"/>
     </row>
     <row r="43" ht="14" customHeight="1"/>
     <row r="44" ht="26" customHeight="1">
-      <c r="A44" s="61" t="inlineStr">
+      <c r="A44" s="79" t="inlineStr">
         <is>
           <t>Three months remaining in original MSA term after December (Jan, Feb, Mar 2026); January is billed on standard cadence.</t>
         </is>
       </c>
-      <c r="B44" s="62" t="n"/>
-      <c r="C44" s="62" t="n"/>
-      <c r="D44" s="62" t="n"/>
-      <c r="E44" s="62" t="n"/>
-      <c r="F44" s="62" t="n"/>
-      <c r="G44" s="62" t="n"/>
-      <c r="H44" s="63" t="n"/>
+      <c r="B44" s="71" t="n"/>
+      <c r="C44" s="71" t="n"/>
+      <c r="D44" s="71" t="n"/>
+      <c r="E44" s="71" t="n"/>
+      <c r="F44" s="71" t="n"/>
+      <c r="G44" s="71" t="n"/>
+      <c r="H44" s="80" t="n"/>
     </row>
     <row r="45" ht="14" customHeight="1"/>
     <row r="46" ht="26" customHeight="1">
-      <c r="A46" s="21" t="inlineStr">
+      <c r="A46" s="68" t="inlineStr">
         <is>
           <t>Remittance &amp; Reference</t>
         </is>
       </c>
-      <c r="B46" s="22" t="n"/>
-      <c r="C46" s="22" t="n"/>
-      <c r="D46" s="22" t="n"/>
-      <c r="E46" s="22" t="n"/>
-      <c r="F46" s="22" t="n"/>
-      <c r="G46" s="22" t="n"/>
-      <c r="H46" s="23" t="n"/>
+      <c r="B46" s="69" t="n"/>
+      <c r="C46" s="69" t="n"/>
+      <c r="D46" s="69" t="n"/>
+      <c r="E46" s="69" t="n"/>
+      <c r="F46" s="69" t="n"/>
+      <c r="G46" s="69" t="n"/>
+      <c r="H46" s="70" t="n"/>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="64" t="inlineStr">
@@ -1894,13 +2079,6 @@
           <t>• Remit to: Thornfield Life Sciences Marketing, Inc., Attn: Accounts Receivable, 227 Alexander Drive, Suite 400, Durham, NC 27709</t>
         </is>
       </c>
-      <c r="B47" s="64" t="n"/>
-      <c r="C47" s="64" t="n"/>
-      <c r="D47" s="64" t="n"/>
-      <c r="E47" s="64" t="n"/>
-      <c r="F47" s="64" t="n"/>
-      <c r="G47" s="64" t="n"/>
-      <c r="H47" s="64" t="n"/>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="64" t="inlineStr">
@@ -1908,13 +2086,6 @@
           <t>• ERPNext Sales Order: SO-2025-0417</t>
         </is>
       </c>
-      <c r="B48" s="64" t="n"/>
-      <c r="C48" s="64" t="n"/>
-      <c r="D48" s="64" t="n"/>
-      <c r="E48" s="64" t="n"/>
-      <c r="F48" s="64" t="n"/>
-      <c r="G48" s="64" t="n"/>
-      <c r="H48" s="64" t="n"/>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="64" t="inlineStr">
@@ -1922,13 +2093,6 @@
           <t>• ERPNext Customer ID: CUST-2025-0198</t>
         </is>
       </c>
-      <c r="B49" s="64" t="n"/>
-      <c r="C49" s="64" t="n"/>
-      <c r="D49" s="64" t="n"/>
-      <c r="E49" s="64" t="n"/>
-      <c r="F49" s="64" t="n"/>
-      <c r="G49" s="64" t="n"/>
-      <c r="H49" s="64" t="n"/>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="64" t="inlineStr">
@@ -1936,13 +2100,6 @@
           <t>• Invoice questions: alan.rutherford@thornfieldlsm.com</t>
         </is>
       </c>
-      <c r="B50" s="64" t="n"/>
-      <c r="C50" s="64" t="n"/>
-      <c r="D50" s="64" t="n"/>
-      <c r="E50" s="64" t="n"/>
-      <c r="F50" s="64" t="n"/>
-      <c r="G50" s="64" t="n"/>
-      <c r="H50" s="64" t="n"/>
     </row>
     <row r="51" ht="14" customHeight="1"/>
     <row r="52" ht="18" customHeight="1">
@@ -1951,13 +2108,6 @@
           <t>Prepared by:</t>
         </is>
       </c>
-      <c r="B52" s="20" t="n"/>
-      <c r="C52" s="20" t="n"/>
-      <c r="D52" s="20" t="n"/>
-      <c r="E52" s="20" t="n"/>
-      <c r="F52" s="20" t="n"/>
-      <c r="G52" s="20" t="n"/>
-      <c r="H52" s="20" t="n"/>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="65" t="inlineStr">
@@ -1965,13 +2115,6 @@
           <t>Alan Rutherford</t>
         </is>
       </c>
-      <c r="B53" s="65" t="n"/>
-      <c r="C53" s="65" t="n"/>
-      <c r="D53" s="65" t="n"/>
-      <c r="E53" s="65" t="n"/>
-      <c r="F53" s="65" t="n"/>
-      <c r="G53" s="65" t="n"/>
-      <c r="H53" s="65" t="n"/>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="66" t="inlineStr">
@@ -1979,13 +2122,6 @@
           <t>Finance Director</t>
         </is>
       </c>
-      <c r="B54" s="66" t="n"/>
-      <c r="C54" s="66" t="n"/>
-      <c r="D54" s="66" t="n"/>
-      <c r="E54" s="66" t="n"/>
-      <c r="F54" s="66" t="n"/>
-      <c r="G54" s="66" t="n"/>
-      <c r="H54" s="66" t="n"/>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="20" t="inlineStr">
@@ -1993,13 +2129,6 @@
           <t>Thornfield Life Sciences Marketing, Inc.</t>
         </is>
       </c>
-      <c r="B55" s="20" t="n"/>
-      <c r="C55" s="20" t="n"/>
-      <c r="D55" s="20" t="n"/>
-      <c r="E55" s="20" t="n"/>
-      <c r="F55" s="20" t="n"/>
-      <c r="G55" s="20" t="n"/>
-      <c r="H55" s="20" t="n"/>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="67" t="inlineStr">
@@ -2007,13 +2136,6 @@
           <t>alan.rutherford@thornfieldlsm.com</t>
         </is>
       </c>
-      <c r="B56" s="67" t="n"/>
-      <c r="C56" s="67" t="n"/>
-      <c r="D56" s="67" t="n"/>
-      <c r="E56" s="67" t="n"/>
-      <c r="F56" s="67" t="n"/>
-      <c r="G56" s="67" t="n"/>
-      <c r="H56" s="67" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="46">

--- a/filesystem/Finance/Billing/FenwickGenomics_Dec2025_statement.xlsx
+++ b/filesystem/Finance/Billing/FenwickGenomics_Dec2025_statement.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="32">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -193,6 +193,11 @@
       <name val="Segoe UI"/>
       <color rgb="FF334155"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="FF475569"/>
+      <sz val="9.5"/>
     </font>
   </fonts>
   <fills count="12">
@@ -720,7 +725,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -940,6 +945,9 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1275,35 +1283,35 @@
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="20" t="inlineStr">
+      <c r="A3" s="81" t="inlineStr">
         <is>
           <t>227 Alexander Drive, Suite 400</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="81" t="inlineStr">
         <is>
           <t>Durham, NC 27709</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="81" t="inlineStr">
         <is>
           <t>EIN: 47-3812905</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="A6" s="81" t="inlineStr">
         <is>
           <t>Phone: +1 (919) 555-0142</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="81" t="inlineStr">
         <is>
           <t>billing@thornfieldlsm.com</t>
         </is>
@@ -2103,7 +2111,7 @@
     </row>
     <row r="51" ht="14" customHeight="1"/>
     <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="20" t="inlineStr">
+      <c r="A52" s="81" t="inlineStr">
         <is>
           <t>Prepared by:</t>
         </is>
@@ -2124,7 +2132,7 @@
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="20" t="inlineStr">
+      <c r="A55" s="81" t="inlineStr">
         <is>
           <t>Thornfield Life Sciences Marketing, Inc.</t>
         </is>
